--- a/input/mapping/110.OCB_GOLD_TTDL_BPM_VOLUME_XLGDTD_LINH.xlsx
+++ b/input/mapping/110.OCB_GOLD_TTDL_BPM_VOLUME_XLGDTD_LINH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anh Hoang Tram\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="13_ncr:1_{86CB0E10-BC9D-48AB-9C23-5B33740DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC1610D3-7759-41AF-B564-1477856A5F5A}"/>
+  <xr:revisionPtr revIDLastSave="335" documentId="13_ncr:1_{86CB0E10-BC9D-48AB-9C23-5B33740DCCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5961CB01-C367-471B-AFA7-8C2BEB37214E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1530" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{6ED3A366-9DB1-4A99-9778-9C0C12893891}"/>
+    <workbookView xWindow="-28920" yWindow="-1530" windowWidth="29040" windowHeight="15840" xr2:uid="{6ED3A366-9DB1-4A99-9778-9C0C12893891}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="431">
   <si>
     <t>BPM_VOLUME_XLGDTD  —  Data Lineage Mind Map</t>
   </si>
@@ -78,10 +78,10 @@
     <t>BPM_VOLUME_XLGDTD</t>
   </si>
   <si>
-    <t>sat_xl_bao_cao_tong_hop_information</t>
-  </si>
-  <si>
-    <t>sat_xl_bao_cao_tong_hop_detail</t>
+    <t>non_his_sat_xl_bao_cao_tong_hop_information</t>
+  </si>
+  <si>
+    <t>non_his_sat_xl_bao_cao_tong_hop_detail</t>
   </si>
   <si>
     <t>hub_xl_ksgn_chung</t>
@@ -331,7 +331,56 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA dmbpm;
-CREATE OR REPLACE TABLE BPM_VOLUME_XLGDTD AS
+INSERT OVERWRITE BPM_VOLUME_XLGDTD
+(
+    MA_GIAO_DICH, MA_GD_GOC, MA_GD_PD, TEN_KHACH_HANG, SO_CIF, SO_DKKD_CMND, LOAI_KHACH_HANG,
+    DVKD_KHOI_TAO, KHOI_KD, LOAI_QUY_TRINH, LOAI_GIAO_DICH, HINH_THUC_CAP_TD, LOAI_SAN_PHAM,
+    LOAI_TSBD, SO_LUONG_TSBD, TONG_RRTD_100_TIEN_GUI, TONG_RRTD_KHAC100_TIEN_GUI, SO_TIEN_GIAO_DICH,
+    SO_LAN_TRINH_PDNL, DON_VI_THUC_HIEN, USER_KHOI_TAO, THOI_GIAN_KHOI_TAO, RM_CUOI_CUNG,
+    DVTD_CUOI_CUNG, TIME_CHUYEN_DVTD_LAN1, CHUYENTV_RM_DVTD, TIME_CHUYENTV_RM_DVTD,
+    TIME_DVTD_YCBS_LAN1, TIME_RM_BS_DVTD_LAN1, TIME_CHUYEN_TDV_LAN1, TEN_TDV_CUOI_CUNG,
+    TDV_YCBS_DVTD, DVTD_YCBS_RM_TU_TDV, RM_BS_DVTD_TU_TDV, DVTD_BS_TDV,
+    TDV_CHUYEN_RM_LAY_Y_KIEN_KH1, RM_DVTD_TSBD_LAN1, TIME_DVTD_TDV_DA_YK_KH,
+    TDV_CHUYEN_RM_LAY_Y_KIEN_KH2, RM_DVTD_TSBD_LAN2, RM_DVTD_TSBD_YCBS_LAN1,
+    DVTD_CHUYEN_TDV_BO_SUNG_TSBD, TDV_RM_TSBD_YCBS_LAN1, RM_DVTD_TSBD_DA_CHINH_SUA,
+    DVTD_RM_TSBD_LAN1, RM_DVTD_TSBD_YCBS_LAN2, DVTD_TDV_TSBD_YCBS_LAN2, TDV_RM_TSBD_YCBS_LAN2,
+    DVTD_RM_TSBD_LAN2, RM_DVTD_TSBD_YCBS_LAN3, DVTD_TDV_TSBD_YCBS_LAN3, TDV_RM_TSBD_YCBS_LAN3,
+    RM_DVTD_TSBD_YCBS_LAN4, DVTD_HOAN_THANH, TRANG_THAI_GIAO_DICH, TIME_CBGDTD_PD_RM, TEN_GDTD,
+    DVTD_GDTD_LAN1, CHUYENTV_DVTD_GDTD, TIME_CHUYENTV_DVTD_GDTD, GDTD_YCBS_DVTD_LAN1,
+    DVTD_RM_BS_TU_GDTD_LAN1, RM_DVTD_YCBS_TU_GDTD_LAN1, DVTD_GDTD_YCBS_TU_GDTD_LAN1,
+    GDTD_YCBS_DVTD_LAN2, DVTD_RM_BS_TU_GDTD_LAN2, RM_DVTD_YCBS_TU_GDTD_LAN2,
+    DVTD_GDTD_YCBS_TU_GDTD_LAN2, GDTD_YCBS_DVTD_LAN3, DVTD_RM_BS_TU_GDTD_LAN3,
+    RM_DVTD_YCBS_TU_GDTD_LAN3, DVTD_GDTD_YCBS_TU_GDTD_LAN3, TEN_KSV_GDTD, CBGDTD_CHUYEN_KSV,
+    GDTD_YCBS_DVTD_YC_TU_KSV, GDTD_DVTD_YCBS_TU_KSV_LAN1, DVTD_RM_YCBS_TU_KSV_LAN1,
+    RM_BS_DVTD_TU_KSV, DVTD_GDTD_TU_KSV, GDTD_BO_SUNG_KSV, KSV_RM_LAY_Y_KIEN_KH_LAN1,
+    KSV_RM_GDTD_LAY_Y_KIEN_KH, GDTD_YC_DVTD_BS_SAU_LAY_Y_KIEN_KH_LAN1,
+    DVTD_YC_BS_THEO_GDTD_SAU_LAY_Y_KIEN_KH_LAN1, RM_BS_DVTD_THEO_GDTD_SAU_LAY_Y_KIEN_KH_LAN1,
+    DVTD_BS_GDTD_SAU_LAY_Y_KIEN_KH_LAN1, GDTD_CHINH_SUA_THEO_KH_LAN1_CHUYEN_KSV,
+    KSV_YC_GDTD_BS_SAU_LAY_Y_KIEN_KH_LAN1, GDTD_YC_DVTD_BS_THEO_KSV_SAU_LAY_Y_KIEN_KH_LAN1,
+    DVTD_RM_YCBS_TU_KSV_LAN2, RM_BS_KSV_KH_YCCS_LAN1, DVTD_GDTD_YCBS_TU_KH_LAN1,
+    GDTD_BO_SUNG_KSV_LAN2, KSV_RM_LAY_Y_KIEN_KH_LAN2, RM_GDTD_YCBS_TU_KH, GDTD_KSV_LAY_Y_KIEN_LAN2,
+    GDTD_YC_DVTD_BS_SAU_LAY_Y_KIEN_KH_LAN2, DVTD_YC_BS_THEO_GDTD_SAU_LAY_Y_KIEN_KH_LAN2,
+    RM_BS_DVTD_THEO_GDTD_SAU_LAY_Y_KIEN_KH_LAN2, DVTD_BS_GDTD_SAU_LAY_Y_KIEN_KH_LAN2,
+    GDTD_CHINH_SUA_THEO_KH_LAN2_CHUYEN_KSV, KSV_YC_GDTD_BS_SAU_LAY_Y_KIEN_KH_LAN2,
+    GDTD_YC_DVTD_BS_THEO_KSV_SAU_LAY_Y_KIEN_KH_LAN2, DVTD_RM_YCBS_TU_KSV_LAN3, RM_BO_SUNG_DVTD_LAN2,
+    DVTD_GDTD_YC_TU_KSV_LAN2, GDTD_BO_SUNG_KSV_LAN3, KSV_RM_LAY_Y_KIEN_KH_LAN3,
+    RM_DVTD_HOAN_THIEN_LAN1, DVTD_CBGDTD_TSBD, GDTD_KSV_TSBD_YCBS_LAN1, DVTD_RM_TSBD_YCBS,
+    RM_DVTD_TSBD_YCBS_LAN5, DVTD_GDTD_TSBD_YCBS, GDTD_KSV_TSBD_YCBS_LAN2, KSV_YCBS_GDTD_TSBD_LAN1,
+    GDTD_DVTD_YCBS_TU_KSV_LAN2, DVTD_YCBS_RM_TSBD, RM_DVTD_YC_TU_KSV_LAN1, DVTD_GDTD_YC_TU_KSV,
+    GDTD_BO_SUNG_KSV_TSBD_LAN1, KSV_RM_TSBD_DA_CHINH_SUA, RM_DVTD_HOAN_THIEN_LAN2,
+    DVTD_GDTD_TSBD_YCBS_LAN2, GDTD_KSV_YCBS_TSBD_LAN1, DVTD_RM_YCBS_TSBD_LAN2,
+    RM_DVTD_YC_TU_KSV_LAN2, RM_DVTD_YC_TU_KSV_LAN3, GDTD_KSV_YCBS_TSBD_LAN2,
+    KSV_YCBS_GDTD_TSBD_LAN2, GDTD_YCBS_DVTD_TSBD_LAN2, DVTD_YCBS_RM_TSBD_LAN2,
+    RM_BO_SUNG_DVTD_YSBS_NHA_NUOC_LAN2, DVTD_GDTD_TU_KSV_LAN2, GDTD_BO_SUNG_KSV_TSBD_LAN2,
+    KSV_RM_TSBD_LAN2, RM_DVTD_HOAN_THIEN, DVTD_RM_KET_QUA_CUOI_CUNG, CBTNTTM, DVTD_CBTNTTTM_LAN1,
+    CHUYENTV_DVTD_CBTNTTTM, TIME_CHUYENTV_DVTD_CBTNTTTM, CBTNTTTM_YCBS_DVTD_LAN1,
+    DVTD_YCBS_RM_TU_CBTNTTM, RM_BS_DVTD_CBTNTTTM_LAN1, DVTD_BO_SUNG_CBTNTTTM_LAN1,
+    CBTNTTTM_CHUYEN_KSVTNTTTM, TEN_KSV_TNTTTM, KSVTNTTTM_YCBS_DVTD, CBTNTTTM_YCBS_DVTD_TU_KSV,
+    DVTD_YCBS_RM_TU_KSVTNTTTM, RM_BO_SUNG_CBTNTTTM_TU_KSV, DVTD_BO_SUNG_CBTNTTTM_LAN2,
+    CBTNTTTM_BO_SUNG_KSVTNTTTM, KSVTNTTTM_CHUYEN_KQ_RM, TEN_KSV_KTHS_QTBSHS, TIME_RM_CHUYEN_CAPPD,
+    TIME_CAPPD_CHUYEN_RM, TIME_RM_BS_CAPPD, LYDO_TUCHOI_DVTD, LYDO_TUCHOI_GDTD, LYDO_TUCHOI_TTTM,
+    GD_TRANG_THAI, NGAY_HOAN_THANH, DATA_DT
+)
 WITH
 bc_inf AS (
     SELECT xl_ksgn_chung_hashkey,
@@ -342,8 +391,8 @@
            so_tien_giao_dich, so_lan_trinh_pdnl,
            user_khoi_tao, thoi_gian_khoi_tao, rm_cuoi_cung, dvtd_cuoi_cung,
            gd_chinh_id, dvkd_khoi_tao, khoi_kd
-    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_xl_bao_cao_tong_hop_information')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    FROM IDENTIFIER(:cleaned || '.raw_vault.non_his_sat_xl_bao_cao_tong_hop_information ')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     QUALIFY ROW_NUMBER() OVER (PARTITION BY xl_ksgn_chung_hashkey
                                ORDER BY source_event_date DESC) = 1
 ),
@@ -407,15 +456,15 @@
            cbtntttm_bo_sung_ksvtntttm, ksvtntttm_chuyen_kq_rm, ten_ksv_kths_qtbshs,
            time_rm_chuyen_cappd, time_cappd_chuyen_rm, time_rm_bs_cappd,
            lydo_tuchoi_dvtd, lydo_tuchoi_gdtd, lydo_tuchoi_tttm
-    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_xl_bao_cao_tong_hop_detail')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    FROM IDENTIFIER(:cleaned || '.raw_vault.non_his_sat_xl_bao_cao_tong_hop_detail')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     QUALIFY ROW_NUMBER() OVER (PARTITION BY xl_ksgn_chung_hashkey
                                ORDER BY source_event_date DESC) = 1
 ),
 h_chung AS (
     SELECT xl_ksgn_chung_hashkey, business_key
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_xl_ksgn_chung')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
 ),
 sat_dv AS (
     SELECT xl_ksgn_chung_hashkey,
@@ -423,7 +472,7 @@
            MAX_BY(ho_so_xu_ly_tai, source_event_date) AS ho_so_xu_ly_tai,
            MAX_BY(ngay_hoan_thanh, source_event_date) AS ngay_hoan_thanh
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_xl_ksgn_chung_don_vi_khoi_tao_phe_duyet')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY xl_ksgn_chung_hashkey
 ),
 sat_tt AS (
@@ -431,7 +480,7 @@
            MAX_BY(gd_trangthai, source_event_date) AS gd_trangthai,
            MAX_BY(trang_thai, source_event_date)   AS trang_thai
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_xl_ksgn_chung_quy_trinh_trang_thai')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY xl_ksgn_chung_hashkey
 ),
 /* = XL_KSGN_CHUNG cua code goc.
@@ -452,13 +501,13 @@
 hub_don_vi AS (
     SELECT auth_to_chuc_don_vi_hashkey, business_key
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_auth_to_chuc_don_vi')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
 ),
 sat_don_vi AS (
     SELECT auth_to_chuc_don_vi_hashkey,
            MAX_BY(ten_don_vi, source_event_date) AS ten_don_vi
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_auth_to_chuc_don_vi')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY auth_to_chuc_don_vi_hashkey
 ),
 /* Chi giu ref_type can dung -&gt; giam kich thuoc broadcast cho 2 lan join */
@@ -469,7 +518,7 @@
            MAX_BY(ref_type, source_event_date) AS ref_type,
            SPLIT(MAX_BY(ref_code, source_event_date), '-')[0] AS ref_code_prefix
     FROM IDENTIFIER(:cleaned || '.raw_vault.ref_bpm_danh_muc')
-    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY ref_hashkey
 ),
 danh_muc_bpm AS (
@@ -481,7 +530,7 @@
     SELECT link_xl_pdtd_link_hashkey,
            MAX_BY(gd_chinh_id, source_event_date) AS gd_chinh_id
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_link_xl_pdtd_link')
-    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
+    WHERE source_event_date = TO_DATE(:target_date, 'yyyyMMdd')
     GROUP BY link_xl_pdtd_link_hashkey
 ),
 link AS (
@@ -490,11 +539,11 @@
     FROM link_sat sl
     JOIN (SELECT link_xl_pdtd_link_hashkey, pdtd_nhom_giao_dich_hashkey
           FROM IDENTIFIER(:cleaned || '.raw_vault.link_xl_pdtd_link')
-          WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')) l
+          WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')) l
       ON l.link_xl_pdtd_link_hashkey = sl.link_xl_pdtd_link_hashkey
     JOIN (SELECT pdtd_nhom_giao_dich_hashkey, business_key
           FROM IDENTIFIER(:cleaned || '.raw_vault.hub_pdtd_nhom_giao_dich')
-          WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')) h_pd
+          WHERE source_event_date &lt;= TO_DATE(:target_date, 'yyyyMMdd')) h_pd
       ON h_pd.pdtd_nhom_giao_dich_hashkey = l.pdtd_nhom_giao_dich_hashkey
     GROUP BY sl.gd_chinh_id
 )
@@ -672,7 +721,7 @@
     bc_detail.LYDO_TUCHOI_TTTM AS LYDO_TUCHOI_TTTM,
     dmTTGD.ten AS GD_TRANG_THAI,
     DATE_FORMAT(CAST(chung.NGAY_HOAN_THANH AS TIMESTAMP), 'dd/MM/yyyy HH:mm:ss') AS NGAY_HOAN_THANH,
-    TO_DATE(:DATADT, 'yyyyMMdd') AS DATA_DT
+    TO_DATE(:target_date, 'yyyyMMdd') AS DATA_DT
 FROM bc_inf
 LEFT JOIN bc_detail   ON bc_inf.xl_ksgn_chung_hashkey = bc_detail.xl_ksgn_chung_hashkey
 LEFT JOIN h_chung     ON bc_inf.xl_ksgn_chung_hashkey = h_chung.xl_ksgn_chung_hashkey
@@ -686,12 +735,12 @@
 LEFT JOIN link        ON TRY_CAST(bc_inf.gd_chinh_id AS BIGINT) = link.gd_chinh_id
 WHERE CAST(bc_inf.THOI_GIAN_KHOI_TAO AS TIMESTAMP) &gt;
           DATE_SUB(
-              ADD_MONTHS(TRUNC(TO_DATE(:DATADT, 'yyyyMMdd'), 'YEAR'), -12),
+              ADD_MONTHS(TRUNC(TO_DATE(:target_date, 'yyyyMMdd'), 'YEAR'), -12),
               1
           )
   AND CAST(chung.NGAY_HOAN_THANH AS TIMESTAMP) &gt;
           DATE_SUB(
-              TRUNC(TO_DATE(:DATADT, 'yyyyMMdd'), 'YEAR'),
+              TRUNC(TO_DATE(:target_date, 'yyyyMMdd'), 'YEAR'),
               1
           )
 AND ((0 = 0) OR (chung.GD_TRANGTHAI = 0))</t>
@@ -729,7 +778,7 @@
            so_tien_giao_dich, so_lan_trinh_pdnl,
            user_khoi_tao, thoi_gian_khoi_tao, rm_cuoi_cung, dvtd_cuoi_cung,
            gd_chinh_id, dvkd_khoi_tao, khoi_kd
-    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_xl_bao_cao_tong_hop_information')
+    FROM IDENTIFIER(:cleaned || '.raw_vault.non_his_sat_xl_bao_cao_tong_hop_information')
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     QUALIFY ROW_NUMBER() OVER (PARTITION BY xl_ksgn_chung_hashkey
                                ORDER BY source_event_date DESC) = 1</t>
@@ -1098,6 +1147,9 @@
   </si>
   <si>
     <t>DATE_FORMAT(CAST(bc_detail.TIME_CHUYEN_DVTD_LAN1 AS TIMESTAMP), 'dd/MM/yyyy HH:mm:ss')</t>
+  </si>
+  <si>
+    <t>sat_xl_bao_cao_tong_hop_detail</t>
   </si>
   <si>
     <t>CHUYENTV_RM_DVTD</t>
@@ -2178,7 +2230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2229,20 +2281,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2262,17 +2308,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
@@ -2641,17 +2690,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.95" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
     </row>
     <row r="2" spans="1:9" ht="36.950000000000003" customHeight="1">
       <c r="A2" s="4" t="s">
@@ -2671,28 +2720,28 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="29" t="s">
+      <c r="G3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -2700,118 +2749,118 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
+      <c r="A4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
       <c r="I4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
+      <c r="A6" s="36"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A7" s="37"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
       <c r="I7" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A8" s="37"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
+      <c r="A8" s="36"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
       <c r="I8" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A9" s="37"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A10" s="37"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A11" s="37"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
+      <c r="A11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.95" customHeight="1">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
+      <c r="A12" s="36"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="6" t="s">
         <v>20</v>
       </c>
@@ -2828,53 +2877,53 @@
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1">
       <c r="A16" s="8"/>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
     </row>
     <row r="17" spans="1:6" ht="15.95" customHeight="1">
       <c r="A17" s="9"/>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
     </row>
     <row r="18" spans="1:6" ht="15.95" customHeight="1">
       <c r="A18" s="10"/>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
     </row>
     <row r="19" spans="1:6" ht="15.95" customHeight="1">
       <c r="A19" s="11"/>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
     </row>
     <row r="20" spans="1:6" ht="15.95" customHeight="1">
       <c r="A20" s="12"/>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2943,7 +2992,7 @@
       <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="24" t="s">
         <v>35</v>
       </c>
       <c r="E3" t="s">
@@ -2969,39 +3018,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="26"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="35"/>
     </row>
     <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="23" t="s">
         <v>43</v>
       </c>
       <c r="F3" s="14"/>
@@ -3235,11 +3284,11 @@
       <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="33"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="35"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="13"/>
       <c r="F17" s="13"/>
     </row>
     <row r="18" spans="1:6">
@@ -3259,14 +3308,14 @@
       <c r="F19" s="13"/>
     </row>
     <row r="20" spans="1:6" ht="18.75">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
     </row>
     <row r="21" spans="1:6" ht="15.75">
       <c r="A21" s="15" t="s">
@@ -3785,7 +3834,7 @@
         <v>145</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -3793,7 +3842,7 @@
         <v>10</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>88</v>
@@ -3802,10 +3851,10 @@
         <v>89</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -3813,7 +3862,7 @@
         <v>10</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>88</v>
@@ -3822,10 +3871,10 @@
         <v>138</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -3833,7 +3882,7 @@
         <v>10</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>88</v>
@@ -3842,10 +3891,10 @@
         <v>138</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3853,7 +3902,7 @@
         <v>10</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>88</v>
@@ -3862,10 +3911,10 @@
         <v>138</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3873,7 +3922,7 @@
         <v>10</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>88</v>
@@ -3882,10 +3931,10 @@
         <v>138</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -3893,7 +3942,7 @@
         <v>10</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>88</v>
@@ -3902,10 +3951,10 @@
         <v>138</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3913,7 +3962,7 @@
         <v>10</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>88</v>
@@ -3922,10 +3971,10 @@
         <v>138</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3933,7 +3982,7 @@
         <v>10</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>88</v>
@@ -3942,10 +3991,10 @@
         <v>138</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -3953,7 +4002,7 @@
         <v>10</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>88</v>
@@ -3962,10 +4011,10 @@
         <v>138</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -3973,7 +4022,7 @@
         <v>10</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>88</v>
@@ -3982,10 +4031,10 @@
         <v>138</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -3993,7 +4042,7 @@
         <v>10</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>88</v>
@@ -4002,10 +4051,10 @@
         <v>138</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -4013,7 +4062,7 @@
         <v>10</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>88</v>
@@ -4022,10 +4071,10 @@
         <v>138</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4033,7 +4082,7 @@
         <v>10</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>88</v>
@@ -4042,10 +4091,10 @@
         <v>138</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4053,7 +4102,7 @@
         <v>10</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>88</v>
@@ -4062,10 +4111,10 @@
         <v>138</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -4073,7 +4122,7 @@
         <v>10</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>88</v>
@@ -4082,10 +4131,10 @@
         <v>138</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -4093,7 +4142,7 @@
         <v>10</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C62" s="17" t="s">
         <v>88</v>
@@ -4102,10 +4151,10 @@
         <v>138</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -4113,7 +4162,7 @@
         <v>10</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C63" s="17" t="s">
         <v>88</v>
@@ -4122,10 +4171,10 @@
         <v>138</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -4133,7 +4182,7 @@
         <v>10</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>88</v>
@@ -4142,10 +4191,10 @@
         <v>138</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -4153,7 +4202,7 @@
         <v>10</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>88</v>
@@ -4162,10 +4211,10 @@
         <v>138</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -4173,7 +4222,7 @@
         <v>10</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C66" s="17" t="s">
         <v>88</v>
@@ -4182,10 +4231,10 @@
         <v>138</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -4193,7 +4242,7 @@
         <v>10</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C67" s="17" t="s">
         <v>88</v>
@@ -4202,10 +4251,10 @@
         <v>138</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -4213,7 +4262,7 @@
         <v>10</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C68" s="17" t="s">
         <v>88</v>
@@ -4222,10 +4271,10 @@
         <v>138</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4233,7 +4282,7 @@
         <v>10</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C69" s="17" t="s">
         <v>88</v>
@@ -4242,10 +4291,10 @@
         <v>138</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4253,7 +4302,7 @@
         <v>10</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>88</v>
@@ -4262,10 +4311,10 @@
         <v>138</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -4273,7 +4322,7 @@
         <v>10</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C71" s="17" t="s">
         <v>88</v>
@@ -4282,10 +4331,10 @@
         <v>138</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4293,7 +4342,7 @@
         <v>10</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C72" s="17" t="s">
         <v>88</v>
@@ -4302,10 +4351,10 @@
         <v>138</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -4313,7 +4362,7 @@
         <v>10</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C73" s="17" t="s">
         <v>88</v>
@@ -4322,10 +4371,10 @@
         <v>138</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4333,7 +4382,7 @@
         <v>10</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C74" s="17" t="s">
         <v>88</v>
@@ -4342,10 +4391,10 @@
         <v>138</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4353,7 +4402,7 @@
         <v>10</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C75" s="17" t="s">
         <v>88</v>
@@ -4362,10 +4411,10 @@
         <v>138</v>
       </c>
       <c r="E75" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -4373,7 +4422,7 @@
         <v>10</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C76" s="17" t="s">
         <v>88</v>
@@ -4382,7 +4431,7 @@
         <v>107</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F76" s="16" t="s">
         <v>18</v>
@@ -4393,7 +4442,7 @@
         <v>10</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C77" s="17" t="s">
         <v>88</v>
@@ -4402,10 +4451,10 @@
         <v>138</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -4413,7 +4462,7 @@
         <v>10</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C78" s="17" t="s">
         <v>88</v>
@@ -4422,10 +4471,10 @@
         <v>89</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -4433,7 +4482,7 @@
         <v>10</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C79" s="17" t="s">
         <v>88</v>
@@ -4442,10 +4491,10 @@
         <v>138</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F79" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -4453,7 +4502,7 @@
         <v>10</v>
       </c>
       <c r="B80" s="16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C80" s="17" t="s">
         <v>88</v>
@@ -4462,10 +4511,10 @@
         <v>89</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -4473,7 +4522,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C81" s="17" t="s">
         <v>88</v>
@@ -4482,10 +4531,10 @@
         <v>138</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -4493,7 +4542,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C82" s="17" t="s">
         <v>88</v>
@@ -4502,10 +4551,10 @@
         <v>138</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -4513,7 +4562,7 @@
         <v>10</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C83" s="17" t="s">
         <v>88</v>
@@ -4522,10 +4571,10 @@
         <v>138</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -4533,7 +4582,7 @@
         <v>10</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C84" s="17" t="s">
         <v>88</v>
@@ -4542,10 +4591,10 @@
         <v>138</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -4553,7 +4602,7 @@
         <v>10</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C85" s="17" t="s">
         <v>88</v>
@@ -4562,10 +4611,10 @@
         <v>138</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -4573,7 +4622,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C86" s="17" t="s">
         <v>88</v>
@@ -4582,10 +4631,10 @@
         <v>138</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -4593,7 +4642,7 @@
         <v>10</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C87" s="17" t="s">
         <v>88</v>
@@ -4602,10 +4651,10 @@
         <v>138</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -4613,7 +4662,7 @@
         <v>10</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C88" s="17" t="s">
         <v>88</v>
@@ -4622,10 +4671,10 @@
         <v>138</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -4633,7 +4682,7 @@
         <v>10</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C89" s="17" t="s">
         <v>88</v>
@@ -4642,10 +4691,10 @@
         <v>138</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -4653,7 +4702,7 @@
         <v>10</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C90" s="17" t="s">
         <v>88</v>
@@ -4662,10 +4711,10 @@
         <v>138</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -4673,7 +4722,7 @@
         <v>10</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C91" s="17" t="s">
         <v>88</v>
@@ -4682,10 +4731,10 @@
         <v>138</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F91" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -4693,7 +4742,7 @@
         <v>10</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C92" s="17" t="s">
         <v>88</v>
@@ -4702,10 +4751,10 @@
         <v>138</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -4713,7 +4762,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C93" s="17" t="s">
         <v>88</v>
@@ -4722,10 +4771,10 @@
         <v>138</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -4733,7 +4782,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C94" s="17" t="s">
         <v>88</v>
@@ -4742,10 +4791,10 @@
         <v>89</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F94" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -4753,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C95" s="17" t="s">
         <v>88</v>
@@ -4762,10 +4811,10 @@
         <v>138</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F95" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -4773,7 +4822,7 @@
         <v>10</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C96" s="17" t="s">
         <v>88</v>
@@ -4782,10 +4831,10 @@
         <v>138</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F96" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -4793,7 +4842,7 @@
         <v>10</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C97" s="17" t="s">
         <v>88</v>
@@ -4802,10 +4851,10 @@
         <v>138</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F97" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -4813,7 +4862,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C98" s="17" t="s">
         <v>88</v>
@@ -4822,10 +4871,10 @@
         <v>138</v>
       </c>
       <c r="E98" s="16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F98" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -4833,7 +4882,7 @@
         <v>10</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C99" s="17" t="s">
         <v>88</v>
@@ -4842,10 +4891,10 @@
         <v>138</v>
       </c>
       <c r="E99" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F99" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -4853,7 +4902,7 @@
         <v>10</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C100" s="17" t="s">
         <v>88</v>
@@ -4862,10 +4911,10 @@
         <v>138</v>
       </c>
       <c r="E100" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -4873,7 +4922,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C101" s="17" t="s">
         <v>88</v>
@@ -4882,10 +4931,10 @@
         <v>138</v>
       </c>
       <c r="E101" s="16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -4893,7 +4942,7 @@
         <v>10</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C102" s="17" t="s">
         <v>88</v>
@@ -4902,10 +4951,10 @@
         <v>138</v>
       </c>
       <c r="E102" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -4913,7 +4962,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C103" s="17" t="s">
         <v>88</v>
@@ -4922,10 +4971,10 @@
         <v>138</v>
       </c>
       <c r="E103" s="16" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -4933,7 +4982,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C104" s="17" t="s">
         <v>88</v>
@@ -4942,10 +4991,10 @@
         <v>138</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -4953,7 +5002,7 @@
         <v>10</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C105" s="17" t="s">
         <v>88</v>
@@ -4962,10 +5011,10 @@
         <v>138</v>
       </c>
       <c r="E105" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -4973,7 +5022,7 @@
         <v>10</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C106" s="17" t="s">
         <v>88</v>
@@ -4982,10 +5031,10 @@
         <v>138</v>
       </c>
       <c r="E106" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F106" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -4993,7 +5042,7 @@
         <v>10</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C107" s="17" t="s">
         <v>88</v>
@@ -5002,10 +5051,10 @@
         <v>138</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F107" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -5013,7 +5062,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C108" s="17" t="s">
         <v>88</v>
@@ -5022,10 +5071,10 @@
         <v>138</v>
       </c>
       <c r="E108" s="16" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F108" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -5033,7 +5082,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C109" s="17" t="s">
         <v>88</v>
@@ -5042,10 +5091,10 @@
         <v>138</v>
       </c>
       <c r="E109" s="16" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F109" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -5053,7 +5102,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C110" s="17" t="s">
         <v>88</v>
@@ -5062,10 +5111,10 @@
         <v>138</v>
       </c>
       <c r="E110" s="16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F110" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -5073,7 +5122,7 @@
         <v>10</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C111" s="17" t="s">
         <v>88</v>
@@ -5082,10 +5131,10 @@
         <v>138</v>
       </c>
       <c r="E111" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F111" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -5093,7 +5142,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C112" s="17" t="s">
         <v>88</v>
@@ -5102,10 +5151,10 @@
         <v>138</v>
       </c>
       <c r="E112" s="16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F112" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -5113,7 +5162,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C113" s="17" t="s">
         <v>88</v>
@@ -5122,10 +5171,10 @@
         <v>138</v>
       </c>
       <c r="E113" s="16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F113" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -5133,7 +5182,7 @@
         <v>10</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C114" s="17" t="s">
         <v>88</v>
@@ -5142,10 +5191,10 @@
         <v>138</v>
       </c>
       <c r="E114" s="16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5153,7 +5202,7 @@
         <v>10</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C115" s="17" t="s">
         <v>88</v>
@@ -5162,10 +5211,10 @@
         <v>138</v>
       </c>
       <c r="E115" s="16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F115" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -5173,7 +5222,7 @@
         <v>10</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C116" s="17" t="s">
         <v>88</v>
@@ -5182,10 +5231,10 @@
         <v>138</v>
       </c>
       <c r="E116" s="16" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F116" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -5193,7 +5242,7 @@
         <v>10</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C117" s="17" t="s">
         <v>88</v>
@@ -5202,10 +5251,10 @@
         <v>138</v>
       </c>
       <c r="E117" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F117" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -5213,7 +5262,7 @@
         <v>10</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C118" s="17" t="s">
         <v>88</v>
@@ -5222,10 +5271,10 @@
         <v>138</v>
       </c>
       <c r="E118" s="16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F118" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -5233,7 +5282,7 @@
         <v>10</v>
       </c>
       <c r="B119" s="16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C119" s="17" t="s">
         <v>88</v>
@@ -5242,10 +5291,10 @@
         <v>138</v>
       </c>
       <c r="E119" s="16" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F119" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -5253,7 +5302,7 @@
         <v>10</v>
       </c>
       <c r="B120" s="16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C120" s="17" t="s">
         <v>88</v>
@@ -5262,10 +5311,10 @@
         <v>138</v>
       </c>
       <c r="E120" s="16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F120" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -5273,7 +5322,7 @@
         <v>10</v>
       </c>
       <c r="B121" s="16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C121" s="17" t="s">
         <v>88</v>
@@ -5282,10 +5331,10 @@
         <v>138</v>
       </c>
       <c r="E121" s="16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F121" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -5293,7 +5342,7 @@
         <v>10</v>
       </c>
       <c r="B122" s="16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C122" s="17" t="s">
         <v>88</v>
@@ -5302,10 +5351,10 @@
         <v>138</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F122" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -5313,7 +5362,7 @@
         <v>10</v>
       </c>
       <c r="B123" s="16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C123" s="17" t="s">
         <v>88</v>
@@ -5322,10 +5371,10 @@
         <v>138</v>
       </c>
       <c r="E123" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F123" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -5333,7 +5382,7 @@
         <v>10</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C124" s="17" t="s">
         <v>88</v>
@@ -5342,10 +5391,10 @@
         <v>138</v>
       </c>
       <c r="E124" s="16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F124" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -5353,7 +5402,7 @@
         <v>10</v>
       </c>
       <c r="B125" s="16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C125" s="17" t="s">
         <v>88</v>
@@ -5362,10 +5411,10 @@
         <v>138</v>
       </c>
       <c r="E125" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5373,7 +5422,7 @@
         <v>10</v>
       </c>
       <c r="B126" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C126" s="17" t="s">
         <v>88</v>
@@ -5382,10 +5431,10 @@
         <v>138</v>
       </c>
       <c r="E126" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -5393,7 +5442,7 @@
         <v>10</v>
       </c>
       <c r="B127" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C127" s="17" t="s">
         <v>88</v>
@@ -5402,10 +5451,10 @@
         <v>138</v>
       </c>
       <c r="E127" s="16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F127" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5413,7 +5462,7 @@
         <v>10</v>
       </c>
       <c r="B128" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C128" s="17" t="s">
         <v>88</v>
@@ -5422,10 +5471,10 @@
         <v>138</v>
       </c>
       <c r="E128" s="16" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F128" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -5433,7 +5482,7 @@
         <v>10</v>
       </c>
       <c r="B129" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C129" s="17" t="s">
         <v>88</v>
@@ -5442,10 +5491,10 @@
         <v>138</v>
       </c>
       <c r="E129" s="16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -5453,7 +5502,7 @@
         <v>10</v>
       </c>
       <c r="B130" s="16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C130" s="17" t="s">
         <v>88</v>
@@ -5462,10 +5511,10 @@
         <v>138</v>
       </c>
       <c r="E130" s="16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F130" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5473,7 +5522,7 @@
         <v>10</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C131" s="17" t="s">
         <v>88</v>
@@ -5482,10 +5531,10 @@
         <v>138</v>
       </c>
       <c r="E131" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F131" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5493,7 +5542,7 @@
         <v>10</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C132" s="17" t="s">
         <v>88</v>
@@ -5502,10 +5551,10 @@
         <v>138</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F132" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5513,7 +5562,7 @@
         <v>10</v>
       </c>
       <c r="B133" s="16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C133" s="17" t="s">
         <v>88</v>
@@ -5522,10 +5571,10 @@
         <v>138</v>
       </c>
       <c r="E133" s="16" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -5533,7 +5582,7 @@
         <v>10</v>
       </c>
       <c r="B134" s="16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C134" s="17" t="s">
         <v>88</v>
@@ -5542,10 +5591,10 @@
         <v>138</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F134" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -5553,7 +5602,7 @@
         <v>10</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C135" s="17" t="s">
         <v>88</v>
@@ -5562,10 +5611,10 @@
         <v>138</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F135" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5573,7 +5622,7 @@
         <v>10</v>
       </c>
       <c r="B136" s="16" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C136" s="17" t="s">
         <v>88</v>
@@ -5582,10 +5631,10 @@
         <v>138</v>
       </c>
       <c r="E136" s="16" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F136" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5593,7 +5642,7 @@
         <v>10</v>
       </c>
       <c r="B137" s="16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C137" s="17" t="s">
         <v>88</v>
@@ -5602,10 +5651,10 @@
         <v>138</v>
       </c>
       <c r="E137" s="16" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F137" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5613,7 +5662,7 @@
         <v>10</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C138" s="17" t="s">
         <v>88</v>
@@ -5622,10 +5671,10 @@
         <v>138</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F138" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5633,7 +5682,7 @@
         <v>10</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C139" s="17" t="s">
         <v>88</v>
@@ -5642,10 +5691,10 @@
         <v>138</v>
       </c>
       <c r="E139" s="16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F139" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -5653,7 +5702,7 @@
         <v>10</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C140" s="17" t="s">
         <v>88</v>
@@ -5662,10 +5711,10 @@
         <v>138</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F140" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -5673,7 +5722,7 @@
         <v>10</v>
       </c>
       <c r="B141" s="16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C141" s="17" t="s">
         <v>88</v>
@@ -5682,10 +5731,10 @@
         <v>138</v>
       </c>
       <c r="E141" s="16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F141" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5693,7 +5742,7 @@
         <v>10</v>
       </c>
       <c r="B142" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C142" s="17" t="s">
         <v>88</v>
@@ -5702,10 +5751,10 @@
         <v>138</v>
       </c>
       <c r="E142" s="16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F142" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5713,7 +5762,7 @@
         <v>10</v>
       </c>
       <c r="B143" s="16" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C143" s="17" t="s">
         <v>88</v>
@@ -5722,10 +5771,10 @@
         <v>138</v>
       </c>
       <c r="E143" s="16" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F143" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5733,7 +5782,7 @@
         <v>10</v>
       </c>
       <c r="B144" s="16" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C144" s="17" t="s">
         <v>88</v>
@@ -5742,10 +5791,10 @@
         <v>138</v>
       </c>
       <c r="E144" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F144" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5753,7 +5802,7 @@
         <v>10</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C145" s="17" t="s">
         <v>88</v>
@@ -5762,10 +5811,10 @@
         <v>138</v>
       </c>
       <c r="E145" s="16" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F145" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5773,7 +5822,7 @@
         <v>10</v>
       </c>
       <c r="B146" s="16" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C146" s="17" t="s">
         <v>88</v>
@@ -5782,10 +5831,10 @@
         <v>138</v>
       </c>
       <c r="E146" s="16" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F146" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5793,19 +5842,19 @@
         <v>10</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C147" s="17" t="s">
         <v>88</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E147" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F147" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -5813,19 +5862,19 @@
         <v>10</v>
       </c>
       <c r="B148" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C148" s="17" t="s">
         <v>88</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E148" s="16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F148" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -5833,19 +5882,19 @@
         <v>10</v>
       </c>
       <c r="B149" s="16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C149" s="17" t="s">
         <v>88</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E149" s="16" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F149" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -5853,7 +5902,7 @@
         <v>10</v>
       </c>
       <c r="B150" s="16" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C150" s="17" t="s">
         <v>88</v>
@@ -5862,10 +5911,10 @@
         <v>138</v>
       </c>
       <c r="E150" s="16" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F150" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5873,7 +5922,7 @@
         <v>10</v>
       </c>
       <c r="B151" s="16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C151" s="17" t="s">
         <v>88</v>
@@ -5882,10 +5931,10 @@
         <v>138</v>
       </c>
       <c r="E151" s="16" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F151" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -5893,7 +5942,7 @@
         <v>10</v>
       </c>
       <c r="B152" s="16" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C152" s="17" t="s">
         <v>88</v>
@@ -5902,10 +5951,10 @@
         <v>138</v>
       </c>
       <c r="E152" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F152" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -5913,7 +5962,7 @@
         <v>10</v>
       </c>
       <c r="B153" s="16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C153" s="17" t="s">
         <v>88</v>
@@ -5922,10 +5971,10 @@
         <v>138</v>
       </c>
       <c r="E153" s="16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F153" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5933,7 +5982,7 @@
         <v>10</v>
       </c>
       <c r="B154" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C154" s="17" t="s">
         <v>88</v>
@@ -5942,10 +5991,10 @@
         <v>138</v>
       </c>
       <c r="E154" s="16" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F154" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5953,7 +6002,7 @@
         <v>10</v>
       </c>
       <c r="B155" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C155" s="17" t="s">
         <v>88</v>
@@ -5962,10 +6011,10 @@
         <v>138</v>
       </c>
       <c r="E155" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F155" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5973,7 +6022,7 @@
         <v>10</v>
       </c>
       <c r="B156" s="16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C156" s="17" t="s">
         <v>88</v>
@@ -5982,10 +6031,10 @@
         <v>138</v>
       </c>
       <c r="E156" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F156" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -5993,7 +6042,7 @@
         <v>10</v>
       </c>
       <c r="B157" s="16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C157" s="17" t="s">
         <v>88</v>
@@ -6002,10 +6051,10 @@
         <v>138</v>
       </c>
       <c r="E157" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F157" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -6013,19 +6062,19 @@
         <v>10</v>
       </c>
       <c r="B158" s="16" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C158" s="17" t="s">
         <v>88</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E158" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F158" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -6033,7 +6082,7 @@
         <v>10</v>
       </c>
       <c r="B159" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C159" s="17" t="s">
         <v>88</v>
@@ -6042,10 +6091,10 @@
         <v>138</v>
       </c>
       <c r="E159" s="16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F159" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -6053,7 +6102,7 @@
         <v>10</v>
       </c>
       <c r="B160" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C160" s="17" t="s">
         <v>88</v>
@@ -6062,10 +6111,10 @@
         <v>89</v>
       </c>
       <c r="E160" s="16" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F160" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -6073,7 +6122,7 @@
         <v>10</v>
       </c>
       <c r="B161" s="16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C161" s="17" t="s">
         <v>88</v>
@@ -6082,10 +6131,10 @@
         <v>138</v>
       </c>
       <c r="E161" s="16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F161" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -6093,7 +6142,7 @@
         <v>10</v>
       </c>
       <c r="B162" s="16" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C162" s="17" t="s">
         <v>88</v>
@@ -6102,10 +6151,10 @@
         <v>89</v>
       </c>
       <c r="E162" s="16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F162" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -6113,7 +6162,7 @@
         <v>10</v>
       </c>
       <c r="B163" s="16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C163" s="17" t="s">
         <v>88</v>
@@ -6122,10 +6171,10 @@
         <v>138</v>
       </c>
       <c r="E163" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F163" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -6133,7 +6182,7 @@
         <v>10</v>
       </c>
       <c r="B164" s="16" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C164" s="17" t="s">
         <v>88</v>
@@ -6142,10 +6191,10 @@
         <v>138</v>
       </c>
       <c r="E164" s="16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F164" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -6153,7 +6202,7 @@
         <v>10</v>
       </c>
       <c r="B165" s="16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C165" s="17" t="s">
         <v>88</v>
@@ -6162,10 +6211,10 @@
         <v>138</v>
       </c>
       <c r="E165" s="16" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F165" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -6173,7 +6222,7 @@
         <v>10</v>
       </c>
       <c r="B166" s="16" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C166" s="17" t="s">
         <v>88</v>
@@ -6182,10 +6231,10 @@
         <v>138</v>
       </c>
       <c r="E166" s="16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F166" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -6193,19 +6242,19 @@
         <v>10</v>
       </c>
       <c r="B167" s="16" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C167" s="17" t="s">
         <v>88</v>
       </c>
       <c r="D167" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E167" s="16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F167" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -6213,7 +6262,7 @@
         <v>10</v>
       </c>
       <c r="B168" s="16" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C168" s="17" t="s">
         <v>88</v>
@@ -6222,10 +6271,10 @@
         <v>138</v>
       </c>
       <c r="E168" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F168" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -6233,7 +6282,7 @@
         <v>10</v>
       </c>
       <c r="B169" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C169" s="17" t="s">
         <v>88</v>
@@ -6242,10 +6291,10 @@
         <v>89</v>
       </c>
       <c r="E169" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F169" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -6253,7 +6302,7 @@
         <v>10</v>
       </c>
       <c r="B170" s="16" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C170" s="17" t="s">
         <v>88</v>
@@ -6262,10 +6311,10 @@
         <v>138</v>
       </c>
       <c r="E170" s="16" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F170" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -6273,7 +6322,7 @@
         <v>10</v>
       </c>
       <c r="B171" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C171" s="17" t="s">
         <v>88</v>
@@ -6282,10 +6331,10 @@
         <v>138</v>
       </c>
       <c r="E171" s="16" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F171" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -6293,7 +6342,7 @@
         <v>10</v>
       </c>
       <c r="B172" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C172" s="17" t="s">
         <v>88</v>
@@ -6302,10 +6351,10 @@
         <v>138</v>
       </c>
       <c r="E172" s="16" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F172" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -6313,7 +6362,7 @@
         <v>10</v>
       </c>
       <c r="B173" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C173" s="17" t="s">
         <v>88</v>
@@ -6322,10 +6371,10 @@
         <v>138</v>
       </c>
       <c r="E173" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F173" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -6333,7 +6382,7 @@
         <v>10</v>
       </c>
       <c r="B174" s="16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C174" s="17" t="s">
         <v>88</v>
@@ -6342,10 +6391,10 @@
         <v>138</v>
       </c>
       <c r="E174" s="16" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F174" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -6353,7 +6402,7 @@
         <v>10</v>
       </c>
       <c r="B175" s="16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C175" s="17" t="s">
         <v>88</v>
@@ -6362,10 +6411,10 @@
         <v>138</v>
       </c>
       <c r="E175" s="16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F175" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -6373,7 +6422,7 @@
         <v>10</v>
       </c>
       <c r="B176" s="16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C176" s="17" t="s">
         <v>88</v>
@@ -6382,10 +6431,10 @@
         <v>138</v>
       </c>
       <c r="E176" s="16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F176" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -6393,7 +6442,7 @@
         <v>10</v>
       </c>
       <c r="B177" s="16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C177" s="17" t="s">
         <v>88</v>
@@ -6402,10 +6451,10 @@
         <v>89</v>
       </c>
       <c r="E177" s="16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F177" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -6413,7 +6462,7 @@
         <v>10</v>
       </c>
       <c r="B178" s="16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C178" s="17" t="s">
         <v>88</v>
@@ -6422,10 +6471,10 @@
         <v>138</v>
       </c>
       <c r="E178" s="16" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F178" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -6433,7 +6482,7 @@
         <v>10</v>
       </c>
       <c r="B179" s="16" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C179" s="17" t="s">
         <v>88</v>
@@ -6442,10 +6491,10 @@
         <v>138</v>
       </c>
       <c r="E179" s="16" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F179" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -6453,7 +6502,7 @@
         <v>10</v>
       </c>
       <c r="B180" s="16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C180" s="17" t="s">
         <v>88</v>
@@ -6462,10 +6511,10 @@
         <v>138</v>
       </c>
       <c r="E180" s="16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F180" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -6473,7 +6522,7 @@
         <v>10</v>
       </c>
       <c r="B181" s="16" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C181" s="17" t="s">
         <v>88</v>
@@ -6482,10 +6531,10 @@
         <v>89</v>
       </c>
       <c r="E181" s="16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F181" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -6493,7 +6542,7 @@
         <v>10</v>
       </c>
       <c r="B182" s="16" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C182" s="17" t="s">
         <v>88</v>
@@ -6502,10 +6551,10 @@
         <v>89</v>
       </c>
       <c r="E182" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F182" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -6513,7 +6562,7 @@
         <v>10</v>
       </c>
       <c r="B183" s="16" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C183" s="17" t="s">
         <v>88</v>
@@ -6522,10 +6571,10 @@
         <v>89</v>
       </c>
       <c r="E183" s="16" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F183" s="16" t="s">
-        <v>12</v>
+        <v>146</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -6533,7 +6582,7 @@
         <v>10</v>
       </c>
       <c r="B184" s="16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C184" s="17" t="s">
         <v>88</v>
@@ -6542,7 +6591,7 @@
         <v>107</v>
       </c>
       <c r="E184" s="16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F184" s="16" t="s">
         <v>18</v>
@@ -6553,16 +6602,16 @@
         <v>10</v>
       </c>
       <c r="B185" s="16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C185" s="17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D185" s="17" t="s">
         <v>138</v>
       </c>
       <c r="E185" s="16" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F185" s="16" t="s">
         <v>14</v>
@@ -6573,19 +6622,19 @@
         <v>10</v>
       </c>
       <c r="B186" s="16" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C186" s="17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D186" s="17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E186" s="16" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F186" s="16" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
